--- a/data/stats_jardin_globale/SURFACE_TOTALE_ET_NOMBRE_JARDINS.xlsx
+++ b/data/stats_jardin_globale/SURFACE_TOTALE_ET_NOMBRE_JARDINS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antoi\Documents\VSC Carte Jardin Strasbourg\data\stats_jardin_globale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF76CF4-DAFE-4E4A-92EF-427AB58DF374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3575A0-A1D9-49A3-B419-ABB2838B8205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JARDINS FAMILIAUX" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="210">
   <si>
     <t>FID</t>
   </si>
@@ -57,15 +57,9 @@
     <t>SURPERFICIE M2</t>
   </si>
   <si>
-    <t>Kleingärten</t>
-  </si>
-  <si>
     <t>LES CEDRES</t>
   </si>
   <si>
-    <t>KLEINGARTENANLAGE</t>
-  </si>
-  <si>
     <t>CITÉ WESTHOFFEN</t>
   </si>
   <si>
@@ -187,9 +181,6 @@
   </si>
   <si>
     <t>JARDINS FAMILIAUX DU CHÂTELET DE LA FORÊT</t>
-  </si>
-  <si>
-    <t>GÄRTNEREI</t>
   </si>
   <si>
     <t>ROEDERSFELD</t>
@@ -688,8 +679,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -738,7 +730,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -766,19 +758,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -823,17 +802,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -846,22 +814,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -875,14 +832,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1012,8 +968,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C41B20EB-E91C-4905-BCB3-0F0148964832}" name="Tableau2" displayName="Tableau2" ref="A1:D216" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
-  <autoFilter ref="A1:D216" xr:uid="{C41B20EB-E91C-4905-BCB3-0F0148964832}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C41B20EB-E91C-4905-BCB3-0F0148964832}" name="Tableau2" displayName="Tableau2" ref="A1:D199" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:D199" xr:uid="{C41B20EB-E91C-4905-BCB3-0F0148964832}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D216">
     <sortCondition ref="A1:A216"/>
   </sortState>
@@ -1290,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:I219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.7265625" customWidth="1"/>
@@ -1300,16 +1256,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1317,2978 +1273,2839 @@
       <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>2026</v>
       </c>
-      <c r="D2" s="9">
-        <v>25400.673805538561</v>
+      <c r="D2">
+        <v>8735.6730622537434</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1">
         <v>2026</v>
       </c>
-      <c r="D3" s="9">
-        <v>8735.6730622537434</v>
+      <c r="D3">
+        <v>10199.179247286171</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1">
         <v>2026</v>
       </c>
-      <c r="D4" s="9">
-        <v>3837.7633125502621</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="18">
+      <c r="D4">
+        <v>8043.4402886666358</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="15">
         <f>SUM(Tableau2[SURPERFICIE M2])</f>
-        <v>2227302.7899881979</v>
+        <v>2063689.2722669034</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C5" s="1">
         <v>2026</v>
       </c>
-      <c r="D5" s="9">
-        <v>10199.179247286171</v>
+      <c r="D5">
+        <v>6153.4257395956674</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
+      <c r="B6" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="1">
         <v>2026</v>
       </c>
-      <c r="D6" s="9">
-        <v>8043.4402886666358</v>
+      <c r="D6">
+        <v>3461.603946179152</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
       <c r="C7" s="1">
         <v>2026</v>
       </c>
-      <c r="D7" s="9">
-        <v>6153.4257395956674</v>
+      <c r="D7">
+        <v>3823.4797431956981</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1">
         <v>2026</v>
       </c>
-      <c r="D8" s="9">
-        <v>3461.603946179152</v>
+      <c r="D8">
+        <v>2279.8535755798221</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>2026</v>
       </c>
-      <c r="D9" s="9">
-        <v>3823.4797431956981</v>
+      <c r="D9">
+        <v>67308.304372541694</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>2026</v>
       </c>
-      <c r="D10" s="9">
-        <v>2279.8535755798221</v>
+      <c r="D10">
+        <v>2762.4048489155248</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>2026</v>
       </c>
-      <c r="D11" s="9">
-        <v>67308.304372541694</v>
+      <c r="D11">
+        <v>5570.2212836095132</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C12" s="1">
         <v>2026</v>
       </c>
-      <c r="D12" s="9">
-        <v>2762.4048489155248</v>
+      <c r="D12">
+        <v>4629.189833828912</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
+      <c r="B13" t="s">
+        <v>13</v>
       </c>
       <c r="C13" s="1">
         <v>2026</v>
       </c>
-      <c r="D13" s="9">
-        <v>5570.2212836095132</v>
+      <c r="D13">
+        <v>1384.365997828543</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
       <c r="C14" s="1">
         <v>2026</v>
       </c>
-      <c r="D14" s="9">
-        <v>4629.189833828912</v>
+      <c r="D14">
+        <v>4784.8353375402658</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
       </c>
-      <c r="D15" s="9">
-        <v>1384.365997828543</v>
+      <c r="D15">
+        <v>3762.4369438365102</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C16" s="1">
         <v>2026</v>
       </c>
-      <c r="D16" s="9">
-        <v>4784.8353375402658</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <v>56674.990815925237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>17</v>
+      <c r="B17" t="s">
+        <v>16</v>
       </c>
       <c r="C17" s="1">
         <v>2026</v>
       </c>
-      <c r="D17" s="9">
-        <v>3762.4369438365102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <v>4979.3908436982747</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
       <c r="C18" s="1">
         <v>2026</v>
       </c>
-      <c r="D18" s="9">
-        <v>56674.990815925237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>2648.6871191345849</v>
+      </c>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="C19" s="1">
         <v>2026</v>
       </c>
-      <c r="D19" s="9">
-        <v>4979.3908436982747</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>1015.247102916623</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C20" s="1">
         <v>2026</v>
       </c>
-      <c r="D20" s="9">
-        <v>2648.6871191345849</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>2895.901889071974</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
       <c r="C21" s="1">
         <v>2026</v>
       </c>
-      <c r="D21" s="9">
-        <v>1015.247102916623</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D21">
+        <v>1780.0209940839561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
       <c r="C22" s="1">
         <v>2026</v>
       </c>
-      <c r="D22" s="9">
-        <v>2895.901889071974</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D22">
+        <v>5100.7187026103566</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>20</v>
+      <c r="B23" t="s">
+        <v>19</v>
       </c>
       <c r="C23" s="1">
         <v>2026</v>
       </c>
-      <c r="D23" s="9">
-        <v>1780.0209940839561</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D23">
+        <v>5036.0597910066208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
       <c r="C24" s="1">
         <v>2026</v>
       </c>
-      <c r="D24" s="9">
-        <v>5100.7187026103566</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D24">
+        <v>9804.9668357074261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>21</v>
+      <c r="B25" t="s">
+        <v>20</v>
       </c>
       <c r="C25" s="1">
         <v>2026</v>
       </c>
-      <c r="D25" s="9">
-        <v>5036.0597910066208</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D25">
+        <v>5129.9201594723854</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C26" s="1">
         <v>2026</v>
       </c>
-      <c r="D26" s="9">
-        <v>9804.9668357074261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D26">
+        <v>1501.2597514055669</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>22</v>
+      <c r="B27" t="s">
+        <v>21</v>
       </c>
       <c r="C27" s="1">
         <v>2026</v>
       </c>
-      <c r="D27" s="9">
-        <v>5129.9201594723854</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D27">
+        <v>11008.10037687421</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
       <c r="C28" s="1">
         <v>2026</v>
       </c>
-      <c r="D28" s="9">
-        <v>1501.2597514055669</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D28">
+        <v>7131.5719922967264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="1">
         <v>2026</v>
       </c>
-      <c r="D29" s="9">
-        <v>11008.10037687421</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D29">
+        <v>1662.1751025989649</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>24</v>
+      <c r="B30" t="s">
+        <v>11</v>
       </c>
       <c r="C30" s="1">
         <v>2026</v>
       </c>
-      <c r="D30" s="9">
-        <v>7131.5719922967264</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D30">
+        <v>1451.7270881906149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>25</v>
+      <c r="B31" t="s">
+        <v>24</v>
       </c>
       <c r="C31" s="1">
         <v>2026</v>
       </c>
-      <c r="D31" s="9">
-        <v>1662.1751025989649</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D31">
+        <v>590.14974122308195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>13</v>
+      <c r="B32" t="s">
+        <v>25</v>
       </c>
       <c r="C32" s="1">
         <v>2026</v>
       </c>
-      <c r="D32" s="9">
-        <v>1451.7270881906149</v>
+      <c r="D32">
+        <v>719.65430953912437</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>26</v>
+      <c r="B33" t="s">
+        <v>24</v>
       </c>
       <c r="C33" s="1">
         <v>2026</v>
       </c>
-      <c r="D33" s="9">
-        <v>590.14974122308195</v>
+      <c r="D33">
+        <v>1619.329053617548</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>27</v>
+      <c r="B34" t="s">
+        <v>26</v>
       </c>
       <c r="C34" s="1">
         <v>2026</v>
       </c>
-      <c r="D34" s="9">
-        <v>719.65430953912437</v>
+      <c r="D34">
+        <v>9417.4903553985059</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>26</v>
+      <c r="B35" t="s">
+        <v>13</v>
       </c>
       <c r="C35" s="1">
         <v>2026</v>
       </c>
-      <c r="D35" s="9">
-        <v>1619.329053617548</v>
+      <c r="D35">
+        <v>2221.5743971094489</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>28</v>
+      <c r="B36" t="s">
+        <v>27</v>
       </c>
       <c r="C36" s="1">
         <v>2026</v>
       </c>
-      <c r="D36" s="9">
-        <v>9417.4903553985059</v>
+      <c r="D36">
+        <v>16498.751316044811</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>15</v>
+      <c r="B37" t="s">
+        <v>28</v>
       </c>
       <c r="C37" s="1">
         <v>2026</v>
       </c>
-      <c r="D37" s="9">
-        <v>2221.5743971094489</v>
+      <c r="D37">
+        <v>4785.5165192913264</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>29</v>
+      <c r="B38" t="s">
+        <v>9</v>
       </c>
       <c r="C38" s="1">
         <v>2026</v>
       </c>
-      <c r="D38" s="9">
-        <v>16498.751316044811</v>
+      <c r="D38">
+        <v>38327.409340141312</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C39" s="1">
         <v>2026</v>
       </c>
-      <c r="D39" s="9">
-        <v>4785.5165192913264</v>
+      <c r="D39">
+        <v>3595.4136153599252</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>11</v>
+      <c r="B40" t="s">
+        <v>29</v>
       </c>
       <c r="C40" s="1">
         <v>2026</v>
       </c>
-      <c r="D40" s="9">
-        <v>38327.409340141312</v>
+      <c r="D40">
+        <v>1924.3987777130681</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>40</v>
       </c>
-      <c r="B41" s="1"/>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
       <c r="C41" s="1">
         <v>2026</v>
       </c>
-      <c r="D41" s="9">
-        <v>3595.4136153599252</v>
+      <c r="D41">
+        <v>1457.460313767195</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="1">
         <v>2026</v>
       </c>
-      <c r="D42" s="9">
-        <v>1924.3987777130681</v>
+      <c r="D42">
+        <v>3538.9621151442411</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>32</v>
+      <c r="B43" t="s">
+        <v>29</v>
       </c>
       <c r="C43" s="1">
         <v>2026</v>
       </c>
-      <c r="D43" s="9">
-        <v>1457.460313767195</v>
+      <c r="D43">
+        <v>3029.213959059678</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>33</v>
+      <c r="B44" t="s">
+        <v>15</v>
       </c>
       <c r="C44" s="1">
         <v>2026</v>
       </c>
-      <c r="D44" s="9">
-        <v>3538.9621151442411</v>
+      <c r="D44">
+        <v>3891.7110469471659</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>31</v>
+      <c r="B45" t="s">
+        <v>32</v>
       </c>
       <c r="C45" s="1">
         <v>2026</v>
       </c>
-      <c r="D45" s="9">
-        <v>3029.213959059678</v>
+      <c r="D45">
+        <v>11583.53917777177</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>17</v>
+      <c r="B46" t="s">
+        <v>33</v>
       </c>
       <c r="C46" s="1">
         <v>2026</v>
       </c>
-      <c r="D46" s="9">
-        <v>3891.7110469471659</v>
+      <c r="D46">
+        <v>817.69524378329515</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>34</v>
+      <c r="B47" t="s">
+        <v>7</v>
       </c>
       <c r="C47" s="1">
         <v>2026</v>
       </c>
-      <c r="D47" s="9">
-        <v>11583.53917777177</v>
+      <c r="D47">
+        <v>2894.5880966838449</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>35</v>
+      <c r="B48" t="s">
+        <v>34</v>
       </c>
       <c r="C48" s="1">
         <v>2026</v>
       </c>
-      <c r="D48" s="9">
-        <v>817.69524378329515</v>
+      <c r="D48">
+        <v>4776.2530138045549</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>9</v>
+      <c r="B49" t="s">
+        <v>35</v>
       </c>
       <c r="C49" s="1">
         <v>2026</v>
       </c>
-      <c r="D49" s="9">
-        <v>2894.5880966838449</v>
+      <c r="D49">
+        <v>1024.387515019625</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>36</v>
       </c>
       <c r="C50" s="1">
         <v>2026</v>
       </c>
-      <c r="D50" s="9">
-        <v>4776.2530138045549</v>
+      <c r="D50">
+        <v>2854.7661290774122</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>37</v>
+      <c r="B51" t="s">
+        <v>16</v>
       </c>
       <c r="C51" s="1">
         <v>2026</v>
       </c>
-      <c r="D51" s="9">
-        <v>1024.387515019625</v>
+      <c r="D51">
+        <v>357.92129026772449</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>38</v>
+      <c r="B52" t="s">
+        <v>16</v>
       </c>
       <c r="C52" s="1">
         <v>2026</v>
       </c>
-      <c r="D52" s="9">
-        <v>2854.7661290774122</v>
+      <c r="D52">
+        <v>2034.589653618634</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>18</v>
+      <c r="B53" t="s">
+        <v>37</v>
       </c>
       <c r="C53" s="1">
         <v>2026</v>
       </c>
-      <c r="D53" s="9">
-        <v>357.92129026772449</v>
+      <c r="D53">
+        <v>857.72352036833763</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>53</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>18</v>
+      <c r="B54" t="s">
+        <v>30</v>
       </c>
       <c r="C54" s="1">
         <v>2026</v>
       </c>
-      <c r="D54" s="9">
-        <v>2034.589653618634</v>
+      <c r="D54">
+        <v>3013.1588622443378</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>54</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>39</v>
+      <c r="B55" t="s">
+        <v>38</v>
       </c>
       <c r="C55" s="1">
         <v>2026</v>
       </c>
-      <c r="D55" s="9">
-        <v>857.72352036833763</v>
+      <c r="D55">
+        <v>2251.018460723571</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>32</v>
+      <c r="B56" t="s">
+        <v>39</v>
       </c>
       <c r="C56" s="1">
         <v>2026</v>
       </c>
-      <c r="D56" s="9">
-        <v>3013.1588622443378</v>
+      <c r="D56">
+        <v>1587.6451459543309</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>56</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>40</v>
+      <c r="B57" t="s">
+        <v>39</v>
       </c>
       <c r="C57" s="1">
         <v>2026</v>
       </c>
-      <c r="D57" s="9">
-        <v>2251.018460723571</v>
+      <c r="D57">
+        <v>568.98094573244452</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>57</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>41</v>
+      <c r="B58" t="s">
+        <v>40</v>
       </c>
       <c r="C58" s="1">
         <v>2026</v>
       </c>
-      <c r="D58" s="9">
-        <v>1587.6451459543309</v>
+      <c r="D58">
+        <v>5045.5425907298632</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>58</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>41</v>
       </c>
       <c r="C59" s="1">
         <v>2026</v>
       </c>
-      <c r="D59" s="9">
-        <v>568.98094573244452</v>
+      <c r="D59">
+        <v>7613.6501572881834</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>59</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="1">
         <v>2026</v>
       </c>
-      <c r="D60" s="9">
-        <v>5045.5425907298632</v>
+      <c r="D60">
+        <v>9279.6024685101584</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>60</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="1">
         <v>2026</v>
       </c>
-      <c r="D61" s="9">
-        <v>7613.6501572881834</v>
+      <c r="D61">
+        <v>2441.11970244348</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>61</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>44</v>
       </c>
       <c r="C62" s="1">
         <v>2026</v>
       </c>
-      <c r="D62" s="9">
-        <v>9279.6024685101584</v>
+      <c r="D62">
+        <v>8396.4882077723742</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>62</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C63" s="1">
         <v>2026</v>
       </c>
-      <c r="D63" s="9">
-        <v>2441.11970244348</v>
+      <c r="D63">
+        <v>100.5245754867792</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>63</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>46</v>
+      <c r="B64" t="s">
+        <v>45</v>
       </c>
       <c r="C64" s="1">
         <v>2026</v>
       </c>
-      <c r="D64" s="9">
-        <v>8396.4882077723742</v>
+      <c r="D64">
+        <v>21534.458895218559</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="8">
         <v>64</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
       <c r="C65" s="1">
         <v>2026</v>
       </c>
-      <c r="D65" s="9">
-        <v>100.5245754867792</v>
+      <c r="D65">
+        <v>12330.117894610559</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="8">
         <v>65</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
+      <c r="B66" t="s">
+        <v>15</v>
       </c>
       <c r="C66" s="1">
         <v>2026</v>
       </c>
-      <c r="D66" s="9">
-        <v>34315.457588824123</v>
+      <c r="D66">
+        <v>5470.947491966188</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
         <v>66</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>47</v>
+      <c r="B67" t="s">
+        <v>13</v>
       </c>
       <c r="C67" s="1">
         <v>2026</v>
       </c>
-      <c r="D67" s="9">
-        <v>21534.458895218559</v>
+      <c r="D67">
+        <v>602.2982256449759</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>67</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>17</v>
+      <c r="B68" t="s">
+        <v>46</v>
       </c>
       <c r="C68" s="1">
         <v>2026</v>
       </c>
-      <c r="D68" s="9">
-        <v>12330.117894610559</v>
+      <c r="D68">
+        <v>4511.66721476987</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="8">
         <v>68</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>17</v>
+      <c r="B69" t="s">
+        <v>15</v>
       </c>
       <c r="C69" s="1">
         <v>2026</v>
       </c>
-      <c r="D69" s="9">
-        <v>5470.947491966188</v>
+      <c r="D69">
+        <v>6989.0096856668806</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="8">
         <v>69</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>48</v>
+      <c r="B70" t="s">
+        <v>7</v>
       </c>
       <c r="C70" s="1">
         <v>2026</v>
       </c>
-      <c r="D70" s="9">
-        <v>36215.964682737373</v>
+      <c r="D70">
+        <v>5385.3946111220866</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="8">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>15</v>
+      <c r="B71" t="s">
+        <v>47</v>
       </c>
       <c r="C71" s="1">
         <v>2026</v>
       </c>
-      <c r="D71" s="9">
-        <v>602.2982256449759</v>
+      <c r="D71">
+        <v>42714.354815721243</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="8">
         <v>71</v>
       </c>
-      <c r="B72" s="1"/>
+      <c r="B72" t="s">
+        <v>41</v>
+      </c>
       <c r="C72" s="1">
         <v>2026</v>
       </c>
-      <c r="D72" s="9">
-        <v>15568.10223245248</v>
+      <c r="D72">
+        <v>8960.6411302017514</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="8">
         <v>72</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>49</v>
+      <c r="B73" t="s">
+        <v>48</v>
       </c>
       <c r="C73" s="1">
         <v>2026</v>
       </c>
-      <c r="D73" s="9">
-        <v>4511.66721476987</v>
+      <c r="D73">
+        <v>5330.2481906060129</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="8">
         <v>73</v>
       </c>
-      <c r="B74" s="1"/>
+      <c r="B74" t="s">
+        <v>49</v>
+      </c>
       <c r="C74" s="1">
         <v>2026</v>
       </c>
-      <c r="D74" s="9">
-        <v>6667.8788492496824</v>
+      <c r="D74">
+        <v>25725.770787166319</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="8">
         <v>74</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>4</v>
+      <c r="B75" t="s">
+        <v>50</v>
       </c>
       <c r="C75" s="1">
         <v>2026</v>
       </c>
-      <c r="D75" s="9">
-        <v>3305.804281020537</v>
+      <c r="D75">
+        <v>12141.388237044221</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="8">
         <v>75</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>4</v>
+      <c r="B76" t="s">
+        <v>51</v>
       </c>
       <c r="C76" s="1">
         <v>2026</v>
       </c>
-      <c r="D76" s="9">
-        <v>3710.7227287851269</v>
+      <c r="D76">
+        <v>2728.3253270369019</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="8">
         <v>76</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>4</v>
+      <c r="B77" t="s">
+        <v>15</v>
       </c>
       <c r="C77" s="1">
         <v>2026</v>
       </c>
-      <c r="D77" s="9">
-        <v>984.12491688411683</v>
+      <c r="D77">
+        <v>37508.338729460207</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="8">
         <v>77</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>17</v>
+      <c r="B78" t="s">
+        <v>15</v>
       </c>
       <c r="C78" s="1">
         <v>2026</v>
       </c>
-      <c r="D78" s="9">
-        <v>6989.0096856668806</v>
+      <c r="D78">
+        <v>17560.839726117909</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="8">
         <v>78</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>9</v>
+      <c r="B79" t="s">
+        <v>7</v>
       </c>
       <c r="C79" s="1">
         <v>2026</v>
       </c>
-      <c r="D79" s="9">
-        <v>5385.3946111220866</v>
+      <c r="D79">
+        <v>4872.5843463670462</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="8">
         <v>79</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>4</v>
+      <c r="B80" t="s">
+        <v>52</v>
       </c>
       <c r="C80" s="1">
         <v>2026</v>
       </c>
-      <c r="D80" s="9">
-        <v>1079.1362433163449</v>
+      <c r="D80">
+        <v>29564.875346760269</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="8">
         <v>80</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>50</v>
+      <c r="B81" t="s">
+        <v>53</v>
       </c>
       <c r="C81" s="1">
         <v>2026</v>
       </c>
-      <c r="D81" s="9">
-        <v>42714.354815721243</v>
+      <c r="D81">
+        <v>9429.2492153854109</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="8">
         <v>81</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>43</v>
+      <c r="B82" t="s">
+        <v>54</v>
       </c>
       <c r="C82" s="1">
         <v>2026</v>
       </c>
-      <c r="D82" s="9">
-        <v>8960.6411302017514</v>
+      <c r="D82">
+        <v>9650.9781559785479</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="8">
         <v>82</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>51</v>
+      <c r="B83" t="s">
+        <v>15</v>
       </c>
       <c r="C83" s="1">
         <v>2026</v>
       </c>
-      <c r="D83" s="9">
-        <v>5330.2481906060129</v>
+      <c r="D83">
+        <v>19892.27121248643</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="8">
         <v>83</v>
       </c>
-      <c r="B84" s="1"/>
+      <c r="B84" t="s">
+        <v>7</v>
+      </c>
       <c r="C84" s="1">
         <v>2026</v>
       </c>
-      <c r="D84" s="9">
-        <v>8076.5762178935111</v>
+      <c r="D84">
+        <v>14444.88710770931</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="8">
         <v>84</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>52</v>
+      <c r="B85" t="s">
+        <v>13</v>
       </c>
       <c r="C85" s="1">
         <v>2026</v>
       </c>
-      <c r="D85" s="9">
-        <v>25725.770787166319</v>
+      <c r="D85">
+        <v>11198.89683496207</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="8">
         <v>85</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>53</v>
+      <c r="B86" t="s">
+        <v>44</v>
       </c>
       <c r="C86" s="1">
         <v>2026</v>
       </c>
-      <c r="D86" s="9">
-        <v>12141.388237044221</v>
+      <c r="D86">
+        <v>4363.0922142099589</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="8">
         <v>86</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>54</v>
+      <c r="B87" t="s">
+        <v>55</v>
       </c>
       <c r="C87" s="1">
         <v>2026</v>
       </c>
-      <c r="D87" s="9">
-        <v>2728.3253270369019</v>
+      <c r="D87">
+        <v>5053.9401293024421</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="8">
         <v>87</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>17</v>
+      <c r="B88" t="s">
+        <v>56</v>
       </c>
       <c r="C88" s="1">
         <v>2026</v>
       </c>
-      <c r="D88" s="9">
-        <v>37508.338729460207</v>
+      <c r="D88">
+        <v>33235.24235442502</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="8">
         <v>88</v>
       </c>
-      <c r="B89" s="1"/>
+      <c r="B89" t="s">
+        <v>57</v>
+      </c>
       <c r="C89" s="1">
         <v>2026</v>
       </c>
-      <c r="D89" s="9">
-        <v>11726.577121995861</v>
+      <c r="D89">
+        <v>4109.8583288928494</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="8">
         <v>89</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>17</v>
+      <c r="B90" t="s">
+        <v>47</v>
       </c>
       <c r="C90" s="1">
         <v>2026</v>
       </c>
-      <c r="D90" s="9">
-        <v>17560.839726117909</v>
+      <c r="D90">
+        <v>38915.861657241083</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="8">
         <v>90</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>9</v>
+      <c r="B91" t="s">
+        <v>58</v>
       </c>
       <c r="C91" s="1">
         <v>2026</v>
       </c>
-      <c r="D91" s="9">
-        <v>4872.5843463670462</v>
+      <c r="D91">
+        <v>42985.45003805001</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="8">
         <v>91</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>55</v>
+      <c r="B92" t="s">
+        <v>7</v>
       </c>
       <c r="C92" s="1">
         <v>2026</v>
       </c>
-      <c r="D92" s="9">
-        <v>29564.875346760269</v>
+      <c r="D92">
+        <v>987.92593739892618</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="8">
         <v>92</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>56</v>
+      <c r="B93" t="s">
+        <v>7</v>
       </c>
       <c r="C93" s="1">
         <v>2026</v>
       </c>
-      <c r="D93" s="9">
-        <v>9429.2492153854109</v>
+      <c r="D93">
+        <v>2914.6500240266319</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="8">
         <v>93</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>57</v>
+      <c r="B94" t="s">
+        <v>59</v>
       </c>
       <c r="C94" s="1">
         <v>2026</v>
       </c>
-      <c r="D94" s="9">
-        <v>9650.9781559785479</v>
+      <c r="D94">
+        <v>9579.2841834540595</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="8">
         <v>94</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>17</v>
+      <c r="B95" t="s">
+        <v>60</v>
       </c>
       <c r="C95" s="1">
         <v>2026</v>
       </c>
-      <c r="D95" s="9">
-        <v>19892.27121248643</v>
+      <c r="D95">
+        <v>82226.812072232831</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="8">
         <v>95</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>9</v>
+      <c r="B96" t="s">
+        <v>20</v>
       </c>
       <c r="C96" s="1">
         <v>2026</v>
       </c>
-      <c r="D96" s="9">
-        <v>14444.88710770931</v>
+      <c r="D96">
+        <v>3352.9375874325629</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="8">
         <v>96</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>15</v>
+      <c r="B97" t="s">
+        <v>61</v>
       </c>
       <c r="C97" s="1">
         <v>2026</v>
       </c>
-      <c r="D97" s="9">
-        <v>11198.89683496207</v>
+      <c r="D97">
+        <v>1533.041071971878</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="8">
         <v>97</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>46</v>
+      <c r="B98" t="s">
+        <v>62</v>
       </c>
       <c r="C98" s="1">
         <v>2026</v>
       </c>
-      <c r="D98" s="9">
-        <v>4363.0922142099589</v>
+      <c r="D98">
+        <v>44304.809140816287</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="8">
         <v>98</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>58</v>
+      <c r="B99" t="s">
+        <v>63</v>
       </c>
       <c r="C99" s="1">
         <v>2026</v>
       </c>
-      <c r="D99" s="9">
-        <v>5053.9401293024421</v>
+      <c r="D99">
+        <v>33226.460741601193</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="8">
         <v>99</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>59</v>
+      <c r="B100" t="s">
+        <v>64</v>
       </c>
       <c r="C100" s="1">
         <v>2026</v>
       </c>
-      <c r="D100" s="9">
-        <v>33235.24235442502</v>
+      <c r="D100">
+        <v>57038.151432359358</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="8">
         <v>100</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C101" s="1">
         <v>2026</v>
       </c>
-      <c r="D101" s="9">
-        <v>4109.8583288928494</v>
+      <c r="D101">
+        <v>2799.7312384545799</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="8">
         <v>101</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>50</v>
+      <c r="B102" t="s">
+        <v>65</v>
       </c>
       <c r="C102" s="1">
         <v>2026</v>
       </c>
-      <c r="D102" s="9">
-        <v>38915.861657241083</v>
+      <c r="D102">
+        <v>13862.05612548022</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="8">
         <v>102</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>61</v>
+      <c r="B103" t="s">
+        <v>7</v>
       </c>
       <c r="C103" s="1">
         <v>2026</v>
       </c>
-      <c r="D103" s="9">
-        <v>42985.45003805001</v>
+      <c r="D103">
+        <v>2216.7099082853379</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="8">
         <v>103</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>9</v>
+      <c r="B104" t="s">
+        <v>15</v>
       </c>
       <c r="C104" s="1">
         <v>2026</v>
       </c>
-      <c r="D104" s="9">
-        <v>987.92593739892618</v>
+      <c r="D104">
+        <v>8140.805322682485</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="8">
         <v>104</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>9</v>
+      <c r="B105" t="s">
+        <v>7</v>
       </c>
       <c r="C105" s="1">
         <v>2026</v>
       </c>
-      <c r="D105" s="9">
-        <v>2914.6500240266319</v>
+      <c r="D105">
+        <v>3541.9613516628742</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="8">
         <v>105</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>62</v>
+      <c r="B106" t="s">
+        <v>4</v>
       </c>
       <c r="C106" s="1">
         <v>2026</v>
       </c>
-      <c r="D106" s="9">
-        <v>9579.2841834540595</v>
+      <c r="D106">
+        <v>3898.2708571404219</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="8">
         <v>106</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>63</v>
+      <c r="B107" t="s">
+        <v>66</v>
       </c>
       <c r="C107" s="1">
         <v>2026</v>
       </c>
-      <c r="D107" s="9">
-        <v>82226.812072232831</v>
+      <c r="D107">
+        <v>812.37627110630274</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="8">
         <v>107</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>22</v>
+      <c r="B108" t="s">
+        <v>67</v>
       </c>
       <c r="C108" s="1">
         <v>2026</v>
       </c>
-      <c r="D108" s="9">
-        <v>3352.9375874325629</v>
+      <c r="D108">
+        <v>2289.6370026334189</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="8">
         <v>108</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C109" s="1">
         <v>2026</v>
       </c>
-      <c r="D109" s="9">
-        <v>1533.041071971878</v>
+      <c r="D109">
+        <v>8051.604322768384</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="8">
         <v>109</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>65</v>
+      <c r="B110" t="s">
+        <v>68</v>
       </c>
       <c r="C110" s="1">
         <v>2026</v>
       </c>
-      <c r="D110" s="9">
-        <v>44304.809140816287</v>
+      <c r="D110">
+        <v>17630.940933561531</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="8">
         <v>110</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>66</v>
+      <c r="B111" t="s">
+        <v>15</v>
       </c>
       <c r="C111" s="1">
         <v>2026</v>
       </c>
-      <c r="D111" s="9">
-        <v>33226.460741601193</v>
+      <c r="D111">
+        <v>1812.651837368496</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="8">
         <v>111</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>67</v>
+      <c r="B112" t="s">
+        <v>33</v>
       </c>
       <c r="C112" s="1">
         <v>2026</v>
       </c>
-      <c r="D112" s="9">
-        <v>57038.151432359358</v>
+      <c r="D112">
+        <v>1168.9898441452531</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="8">
         <v>112</v>
       </c>
-      <c r="B113" s="1"/>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
       <c r="C113" s="1">
         <v>2026</v>
       </c>
-      <c r="D113" s="9">
-        <v>5336.772106761724</v>
+      <c r="D113">
+        <v>27902.12535763608</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="8">
         <v>113</v>
       </c>
-      <c r="B114" s="1"/>
+      <c r="B114" t="s">
+        <v>69</v>
+      </c>
       <c r="C114" s="1">
         <v>2026</v>
       </c>
-      <c r="D114" s="9">
-        <v>2799.7312384545799</v>
+      <c r="D114">
+        <v>62059.613344883663</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="8">
         <v>114</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>68</v>
+      <c r="B115" t="s">
+        <v>70</v>
       </c>
       <c r="C115" s="1">
         <v>2026</v>
       </c>
-      <c r="D115" s="9">
-        <v>13862.05612548022</v>
+      <c r="D115">
+        <v>1189.0377415120599</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="8">
         <v>115</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>9</v>
+      <c r="B116" t="s">
+        <v>15</v>
       </c>
       <c r="C116" s="1">
         <v>2026</v>
       </c>
-      <c r="D116" s="9">
-        <v>2216.7099082853379</v>
+      <c r="D116">
+        <v>19750.586982192381</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="8">
         <v>116</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>17</v>
+      <c r="B117" t="s">
+        <v>7</v>
       </c>
       <c r="C117" s="1">
         <v>2026</v>
       </c>
-      <c r="D117" s="9">
-        <v>8140.805322682485</v>
+      <c r="D117">
+        <v>17183.037114270031</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="8">
         <v>117</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>9</v>
+      <c r="B118" t="s">
+        <v>71</v>
       </c>
       <c r="C118" s="1">
         <v>2026</v>
       </c>
-      <c r="D118" s="9">
-        <v>3541.9613516628742</v>
+      <c r="D118">
+        <v>4906.1663170326501</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="8">
         <v>118</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>5</v>
+      <c r="B119" t="s">
+        <v>72</v>
       </c>
       <c r="C119" s="1">
         <v>2026</v>
       </c>
-      <c r="D119" s="9">
-        <v>3898.2708571404219</v>
+      <c r="D119">
+        <v>13867.480485949671</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="8">
         <v>119</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>69</v>
+      <c r="B120" t="s">
+        <v>63</v>
       </c>
       <c r="C120" s="1">
         <v>2026</v>
       </c>
-      <c r="D120" s="9">
-        <v>812.37627110630274</v>
+      <c r="D120">
+        <v>18370.936592741869</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="8">
         <v>120</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>70</v>
+      <c r="B121" t="s">
+        <v>73</v>
       </c>
       <c r="C121" s="1">
         <v>2026</v>
       </c>
-      <c r="D121" s="9">
-        <v>2289.6370026334189</v>
+      <c r="D121">
+        <v>13618.44877207125</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="8">
         <v>121</v>
       </c>
-      <c r="B122" s="1"/>
+      <c r="B122" t="s">
+        <v>74</v>
+      </c>
       <c r="C122" s="1">
         <v>2026</v>
       </c>
-      <c r="D122" s="9">
-        <v>8051.604322768384</v>
+      <c r="D122">
+        <v>14611.83927277476</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="8">
         <v>122</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>71</v>
+      <c r="B123" t="s">
+        <v>75</v>
       </c>
       <c r="C123" s="1">
         <v>2026</v>
       </c>
-      <c r="D123" s="9">
-        <v>17630.940933561531</v>
+      <c r="D123">
+        <v>7318.4764791354537</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="8">
         <v>123</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>17</v>
+      <c r="B124" t="s">
+        <v>76</v>
       </c>
       <c r="C124" s="1">
         <v>2026</v>
       </c>
-      <c r="D124" s="9">
-        <v>1812.651837368496</v>
+      <c r="D124">
+        <v>5316.4146267734468</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="8">
         <v>124</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>35</v>
+      <c r="B125" t="s">
+        <v>77</v>
       </c>
       <c r="C125" s="1">
         <v>2026</v>
       </c>
-      <c r="D125" s="9">
-        <v>1168.9898441452531</v>
+      <c r="D125">
+        <v>89838.705708144422</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="8">
         <v>125</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>33</v>
+      <c r="B126" t="s">
+        <v>15</v>
       </c>
       <c r="C126" s="1">
         <v>2026</v>
       </c>
-      <c r="D126" s="9">
-        <v>27902.12535763608</v>
+      <c r="D126">
+        <v>9849.3767548858305</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="8">
         <v>126</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>72</v>
+      <c r="B127" t="s">
+        <v>78</v>
       </c>
       <c r="C127" s="1">
         <v>2026</v>
       </c>
-      <c r="D127" s="9">
-        <v>62059.613344883663</v>
+      <c r="D127">
+        <v>7739.1765601187944</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="8">
         <v>127</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>73</v>
+      <c r="B128" t="s">
+        <v>29</v>
       </c>
       <c r="C128" s="1">
         <v>2026</v>
       </c>
-      <c r="D128" s="9">
-        <v>1189.0377415120599</v>
+      <c r="D128">
+        <v>1521.117105141049</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="8">
         <v>128</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>17</v>
+      <c r="B129" t="s">
+        <v>15</v>
       </c>
       <c r="C129" s="1">
         <v>2026</v>
       </c>
-      <c r="D129" s="9">
-        <v>19750.586982192381</v>
+      <c r="D129">
+        <v>17301.042652450731</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="8">
         <v>129</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>9</v>
+      <c r="B130" t="s">
+        <v>79</v>
       </c>
       <c r="C130" s="1">
         <v>2026</v>
       </c>
-      <c r="D130" s="9">
-        <v>17183.037114270031</v>
+      <c r="D130">
+        <v>20958.007693772201</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="8">
         <v>130</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>74</v>
+      <c r="B131" t="s">
+        <v>80</v>
       </c>
       <c r="C131" s="1">
         <v>2026</v>
       </c>
-      <c r="D131" s="9">
-        <v>4906.1663170326501</v>
+      <c r="D131">
+        <v>1779.506977872923</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="8">
         <v>131</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>75</v>
+      <c r="B132" t="s">
+        <v>81</v>
       </c>
       <c r="C132" s="1">
         <v>2026</v>
       </c>
-      <c r="D132" s="9">
-        <v>13867.480485949671</v>
+      <c r="D132">
+        <v>4435.272680767579</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="8">
         <v>132</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>66</v>
+      <c r="B133" t="s">
+        <v>19</v>
       </c>
       <c r="C133" s="1">
         <v>2026</v>
       </c>
-      <c r="D133" s="9">
-        <v>18370.936592741869</v>
+      <c r="D133">
+        <v>5526.9108474655077</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="8">
         <v>133</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>76</v>
+      <c r="B134" t="s">
+        <v>25</v>
       </c>
       <c r="C134" s="1">
         <v>2026</v>
       </c>
-      <c r="D134" s="9">
-        <v>13618.44877207125</v>
+      <c r="D134">
+        <v>7362.6828416921198</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="8">
         <v>134</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>77</v>
+      <c r="B135" t="s">
+        <v>82</v>
       </c>
       <c r="C135" s="1">
         <v>2026</v>
       </c>
-      <c r="D135" s="9">
-        <v>14611.83927277476</v>
+      <c r="D135">
+        <v>11178.544233053201</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="8">
         <v>135</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>78</v>
+      <c r="B136" t="s">
+        <v>83</v>
       </c>
       <c r="C136" s="1">
         <v>2026</v>
       </c>
-      <c r="D136" s="9">
-        <v>7318.4764791354537</v>
+      <c r="D136">
+        <v>4252.6891893753782</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="8">
         <v>136</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>79</v>
+      <c r="B137" t="s">
+        <v>15</v>
       </c>
       <c r="C137" s="1">
         <v>2026</v>
       </c>
-      <c r="D137" s="9">
-        <v>5316.4146267734468</v>
+      <c r="D137">
+        <v>12461.60701037943</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="8">
         <v>137</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>80</v>
+      <c r="B138" t="s">
+        <v>15</v>
       </c>
       <c r="C138" s="1">
         <v>2026</v>
       </c>
-      <c r="D138" s="9">
-        <v>89838.705708144422</v>
+      <c r="D138">
+        <v>38247.627833028513</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="8">
         <v>138</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>17</v>
+      <c r="B139" t="s">
+        <v>84</v>
       </c>
       <c r="C139" s="1">
         <v>2026</v>
       </c>
-      <c r="D139" s="9">
-        <v>9849.3767548858305</v>
+      <c r="D139">
+        <v>10569.939222452231</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="8">
         <v>139</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>81</v>
+      <c r="B140" t="s">
+        <v>85</v>
       </c>
       <c r="C140" s="1">
         <v>2026</v>
       </c>
-      <c r="D140" s="9">
-        <v>7739.1765601187944</v>
+      <c r="D140">
+        <v>5819.2624799611513</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="8">
         <v>140</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>31</v>
+      <c r="B141" t="s">
+        <v>34</v>
       </c>
       <c r="C141" s="1">
         <v>2026</v>
       </c>
-      <c r="D141" s="9">
-        <v>1521.117105141049</v>
+      <c r="D141">
+        <v>1315.242941398174</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="8">
         <v>141</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>17</v>
+      <c r="B142" t="s">
+        <v>13</v>
       </c>
       <c r="C142" s="1">
         <v>2026</v>
       </c>
-      <c r="D142" s="9">
-        <v>17301.042652450731</v>
+      <c r="D142">
+        <v>2064.8994207195942</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="8">
         <v>142</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>82</v>
+      <c r="B143" t="s">
+        <v>13</v>
       </c>
       <c r="C143" s="1">
         <v>2026</v>
       </c>
-      <c r="D143" s="9">
-        <v>20958.007693772201</v>
+      <c r="D143">
+        <v>966.32158205285668</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="8">
         <v>143</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="C144" s="1">
         <v>2026</v>
       </c>
-      <c r="D144" s="9">
-        <v>1779.506977872923</v>
+      <c r="D144">
+        <v>873.40106604620814</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="8">
         <v>144</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>84</v>
+      <c r="B145" t="s">
+        <v>86</v>
       </c>
       <c r="C145" s="1">
         <v>2026</v>
       </c>
-      <c r="D145" s="9">
-        <v>4435.272680767579</v>
+      <c r="D145">
+        <v>777.04740397632122</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="8">
         <v>145</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>21</v>
+      <c r="B146" t="s">
+        <v>15</v>
       </c>
       <c r="C146" s="1">
         <v>2026</v>
       </c>
-      <c r="D146" s="9">
-        <v>5526.9108474655077</v>
+      <c r="D146">
+        <v>11033.19476863085</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="8">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="C147" s="1">
         <v>2026</v>
       </c>
-      <c r="D147" s="9">
-        <v>7362.6828416921198</v>
+      <c r="D147">
+        <v>1757.904325529933</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="8">
         <v>147</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>85</v>
+      <c r="B148" t="s">
+        <v>87</v>
       </c>
       <c r="C148" s="1">
         <v>2026</v>
       </c>
-      <c r="D148" s="9">
-        <v>11178.544233053201</v>
+      <c r="D148">
+        <v>414.28128709644079</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="8">
         <v>148</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>86</v>
+      <c r="B149" t="s">
+        <v>88</v>
       </c>
       <c r="C149" s="1">
         <v>2026</v>
       </c>
-      <c r="D149" s="9">
-        <v>4252.6891893753782</v>
+      <c r="D149">
+        <v>37602.974800044212</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="8">
         <v>149</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>17</v>
+      <c r="B150" t="s">
+        <v>15</v>
       </c>
       <c r="C150" s="1">
         <v>2026</v>
       </c>
-      <c r="D150" s="9">
-        <v>12461.60701037943</v>
+      <c r="D150">
+        <v>5413.7285466082394</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="8">
         <v>150</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>17</v>
+      <c r="B151" t="s">
+        <v>7</v>
       </c>
       <c r="C151" s="1">
         <v>2026</v>
       </c>
-      <c r="D151" s="9">
-        <v>38247.627833028513</v>
+      <c r="D151">
+        <v>1827.1812510131861</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="8">
         <v>151</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>87</v>
+      <c r="B152" t="s">
+        <v>89</v>
       </c>
       <c r="C152" s="1">
         <v>2026</v>
       </c>
-      <c r="D152" s="9">
-        <v>10569.939222452231</v>
+      <c r="D152">
+        <v>23354.479791779941</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="8">
         <v>152</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>4</v>
+      <c r="B153" t="s">
+        <v>26</v>
       </c>
       <c r="C153" s="1">
         <v>2026</v>
       </c>
-      <c r="D153" s="9">
-        <v>744.5342662287876</v>
+      <c r="D153">
+        <v>26852.462892858279</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="8">
         <v>153</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>88</v>
+      <c r="B154" t="s">
+        <v>90</v>
       </c>
       <c r="C154" s="1">
         <v>2026</v>
       </c>
-      <c r="D154" s="9">
-        <v>5819.2624799611513</v>
+      <c r="D154">
+        <v>27119.451885599989</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="8">
         <v>154</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>36</v>
+      <c r="B155" t="s">
+        <v>91</v>
       </c>
       <c r="C155" s="1">
         <v>2026</v>
       </c>
-      <c r="D155" s="9">
-        <v>1315.242941398174</v>
+      <c r="D155">
+        <v>33623.908508138273</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="8">
         <v>155</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>15</v>
+      <c r="B156" t="s">
+        <v>92</v>
       </c>
       <c r="C156" s="1">
         <v>2026</v>
       </c>
-      <c r="D156" s="9">
-        <v>2064.8994207195942</v>
+      <c r="D156">
+        <v>32836.137255235153</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="8">
         <v>156</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157" s="1">
         <v>2026</v>
       </c>
-      <c r="D157" s="9">
-        <v>966.32158205285668</v>
+      <c r="D157">
+        <v>9241.5004266528413</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="8">
         <v>157</v>
       </c>
-      <c r="B158" s="1"/>
+      <c r="B158" t="s">
+        <v>93</v>
+      </c>
       <c r="C158" s="1">
         <v>2026</v>
       </c>
-      <c r="D158" s="9">
-        <v>873.40106604620814</v>
+      <c r="D158">
+        <v>4104.3966805962846</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="8">
         <v>158</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>89</v>
+      <c r="B159" t="s">
+        <v>15</v>
       </c>
       <c r="C159" s="1">
         <v>2026</v>
       </c>
-      <c r="D159" s="9">
-        <v>777.04740397632122</v>
+      <c r="D159">
+        <v>741.89166027680039</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="8">
         <v>159</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>17</v>
+      <c r="B160" t="s">
+        <v>94</v>
       </c>
       <c r="C160" s="1">
         <v>2026</v>
       </c>
-      <c r="D160" s="9">
-        <v>11033.19476863085</v>
+      <c r="D160">
+        <v>19281.067157775859</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="8">
         <v>160</v>
       </c>
-      <c r="B161" s="1"/>
+      <c r="B161" t="s">
+        <v>19</v>
+      </c>
       <c r="C161" s="1">
         <v>2026</v>
       </c>
-      <c r="D161" s="9">
-        <v>1757.904325529933</v>
+      <c r="D161">
+        <v>21365.662673875569</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="8">
         <v>161</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>90</v>
+      <c r="B162" t="s">
+        <v>7</v>
       </c>
       <c r="C162" s="1">
         <v>2026</v>
       </c>
-      <c r="D162" s="9">
-        <v>414.28128709644079</v>
+      <c r="D162">
+        <v>1609.2623894741989</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="8">
         <v>162</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>91</v>
+      <c r="B163" t="s">
+        <v>95</v>
       </c>
       <c r="C163" s="1">
         <v>2026</v>
       </c>
-      <c r="D163" s="9">
-        <v>37602.974800044212</v>
+      <c r="D163">
+        <v>639.64635649323463</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" s="8">
         <v>163</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>17</v>
+      <c r="B164" t="s">
+        <v>96</v>
       </c>
       <c r="C164" s="1">
         <v>2026</v>
       </c>
-      <c r="D164" s="9">
-        <v>5413.7285466082394</v>
+      <c r="D164">
+        <v>5630.5659714179637</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" s="8">
         <v>164</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>4</v>
+      <c r="B165" t="s">
+        <v>97</v>
       </c>
       <c r="C165" s="1">
         <v>2026</v>
       </c>
-      <c r="D165" s="9">
-        <v>1826.0647229477761</v>
+      <c r="D165">
+        <v>3178.502649593167</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="8">
         <v>165</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>9</v>
+      <c r="B166" t="s">
+        <v>98</v>
       </c>
       <c r="C166" s="1">
         <v>2026</v>
       </c>
-      <c r="D166" s="9">
-        <v>1827.1812510131861</v>
+      <c r="D166">
+        <v>1315.496799241751</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" s="8">
         <v>166</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>92</v>
+      <c r="B167" t="s">
+        <v>99</v>
       </c>
       <c r="C167" s="1">
         <v>2026</v>
       </c>
-      <c r="D167" s="9">
-        <v>23354.479791779941</v>
+      <c r="D167">
+        <v>557.76786363683641</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" s="8">
         <v>167</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>28</v>
+      <c r="B168" t="s">
+        <v>7</v>
       </c>
       <c r="C168" s="1">
         <v>2026</v>
       </c>
-      <c r="D168" s="9">
-        <v>26852.462892858279</v>
+      <c r="D168">
+        <v>16054.34740018845</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" s="8">
         <v>168</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>93</v>
+      <c r="B169" t="s">
+        <v>101</v>
       </c>
       <c r="C169" s="1">
         <v>2026</v>
       </c>
-      <c r="D169" s="9">
-        <v>27119.451885599989</v>
+      <c r="D169">
+        <v>4329.8482292480767</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="8">
         <v>169</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>94</v>
+      <c r="B170" t="s">
+        <v>102</v>
       </c>
       <c r="C170" s="1">
         <v>2026</v>
       </c>
-      <c r="D170" s="9">
-        <v>33623.908508138273</v>
+      <c r="D170">
+        <v>5831.0929686771706</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" s="8">
         <v>170</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>95</v>
+      <c r="B171" t="s">
+        <v>103</v>
       </c>
       <c r="C171" s="1">
         <v>2026</v>
       </c>
-      <c r="D171" s="9">
-        <v>32836.137255235153</v>
+      <c r="D171">
+        <v>250.5987380743027</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" s="8">
         <v>171</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>17</v>
+      <c r="B172" t="s">
+        <v>80</v>
       </c>
       <c r="C172" s="1">
         <v>2026</v>
       </c>
-      <c r="D172" s="9">
-        <v>9241.5004266528413</v>
+      <c r="D172">
+        <v>2860.1368453651671</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="8">
         <v>172</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>96</v>
+      <c r="B173" t="s">
+        <v>104</v>
       </c>
       <c r="C173" s="1">
         <v>2026</v>
       </c>
-      <c r="D173" s="9">
-        <v>4104.3966805962846</v>
+      <c r="D173">
+        <v>1398.296507300714</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="8">
         <v>173</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>4</v>
+      <c r="B174" t="s">
+        <v>105</v>
       </c>
       <c r="C174" s="1">
         <v>2026</v>
       </c>
-      <c r="D174" s="9">
-        <v>1467.9001945275811</v>
+      <c r="D174">
+        <v>486.1975267753005</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" s="8">
         <v>174</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C175" s="1">
         <v>2026</v>
       </c>
-      <c r="D175" s="9">
-        <v>741.89166027680039</v>
+      <c r="D175">
+        <v>16850.784333020449</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" s="8">
         <v>175</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>97</v>
+      <c r="B176" t="s">
+        <v>15</v>
       </c>
       <c r="C176" s="1">
         <v>2026</v>
       </c>
-      <c r="D176" s="9">
-        <v>19281.067157775859</v>
+      <c r="D176">
+        <v>5014.4822857391546</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" s="8">
         <v>176</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>4</v>
+      <c r="B177" t="s">
+        <v>106</v>
       </c>
       <c r="C177" s="1">
         <v>2026</v>
       </c>
-      <c r="D177" s="9">
-        <v>3349.4644495807588</v>
+      <c r="D177">
+        <v>6971.9766508119646</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" s="8">
         <v>177</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>21</v>
+      <c r="B178" t="s">
+        <v>107</v>
       </c>
       <c r="C178" s="1">
         <v>2026</v>
       </c>
-      <c r="D178" s="9">
-        <v>21365.662673875569</v>
+      <c r="D178">
+        <v>5176.3475103154778</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" s="8">
         <v>178</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>9</v>
+      <c r="B179" t="s">
+        <v>16</v>
       </c>
       <c r="C179" s="1">
         <v>2026</v>
       </c>
-      <c r="D179" s="9">
-        <v>1609.2623894741989</v>
+      <c r="D179">
+        <v>5209.1038375869393</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" s="8">
         <v>179</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>98</v>
+      <c r="B180" t="s">
+        <v>108</v>
       </c>
       <c r="C180" s="1">
         <v>2026</v>
       </c>
-      <c r="D180" s="9">
-        <v>639.64635649323463</v>
+      <c r="D180">
+        <v>1544.6386331543331</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" s="8">
         <v>180</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="C181" s="1">
         <v>2026</v>
       </c>
-      <c r="D181" s="9">
-        <v>5630.5659714179637</v>
+      <c r="D181">
+        <v>11524.26645523775</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" s="8">
         <v>181</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>100</v>
+      <c r="B182" t="s">
+        <v>15</v>
       </c>
       <c r="C182" s="1">
         <v>2026</v>
       </c>
-      <c r="D182" s="9">
-        <v>3178.502649593167</v>
+      <c r="D182">
+        <v>3461.9229219518602</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" s="8">
         <v>182</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>101</v>
+      <c r="B183" t="s">
+        <v>109</v>
       </c>
       <c r="C183" s="1">
         <v>2026</v>
       </c>
-      <c r="D183" s="9">
-        <v>1315.496799241751</v>
+      <c r="D183">
+        <v>223.3704585544765</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" s="8">
         <v>183</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>102</v>
+      <c r="B184" t="s">
+        <v>63</v>
       </c>
       <c r="C184" s="1">
         <v>2026</v>
       </c>
-      <c r="D184" s="9">
-        <v>557.76786363683641</v>
+      <c r="D184">
+        <v>1302.7881271715739</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="8">
         <v>184</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>9</v>
+      <c r="B185" t="s">
+        <v>110</v>
       </c>
       <c r="C185" s="1">
         <v>2026</v>
       </c>
-      <c r="D185" s="9">
-        <v>16054.34740018845</v>
+      <c r="D185">
+        <v>2754.187203912355</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" s="8">
-        <v>186</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>104</v>
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>37</v>
       </c>
       <c r="C186" s="1">
         <v>2026</v>
       </c>
-      <c r="D186" s="9">
-        <v>4329.8482292480767</v>
+      <c r="D186">
+        <v>884.20877583324909</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" s="8">
-        <v>187</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>105</v>
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>111</v>
       </c>
       <c r="C187" s="1">
         <v>2026</v>
       </c>
-      <c r="D187" s="9">
-        <v>5831.0929686771706</v>
+      <c r="D187">
+        <v>522.25835009664297</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" s="8">
-        <v>188</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>106</v>
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>112</v>
       </c>
       <c r="C188" s="1">
         <v>2026</v>
       </c>
-      <c r="D188" s="9">
-        <v>250.5987380743027</v>
+      <c r="D188">
+        <v>1606.22439211607</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" s="8">
-        <v>189</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
       <c r="C189" s="1">
         <v>2026</v>
       </c>
-      <c r="D189" s="9">
-        <v>2860.1368453651671</v>
+      <c r="D189">
+        <v>2116.5112092643981</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" s="8">
-        <v>190</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="C190" s="1">
         <v>2026</v>
       </c>
-      <c r="D190" s="9">
-        <v>1398.296507300714</v>
+      <c r="D190">
+        <v>755.05368263274431</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="8">
-        <v>191</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>108</v>
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>60</v>
       </c>
       <c r="C191" s="1">
         <v>2026</v>
       </c>
-      <c r="D191" s="9">
-        <v>486.1975267753005</v>
+      <c r="D191">
+        <v>40708.200460527092</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="8">
-        <v>192</v>
-      </c>
-      <c r="B192" s="1"/>
+        <v>191</v>
+      </c>
       <c r="C192" s="1">
         <v>2026</v>
       </c>
-      <c r="D192" s="9">
-        <v>16850.784333020449</v>
+      <c r="D192">
+        <v>19216.072628157679</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="8">
-        <v>193</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>17</v>
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>86</v>
       </c>
       <c r="C193" s="1">
         <v>2026</v>
       </c>
-      <c r="D193" s="9">
-        <v>5014.4822857391546</v>
+      <c r="D193">
+        <v>360.23156277835369</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" s="8">
-        <v>194</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>109</v>
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>33</v>
       </c>
       <c r="C194" s="1">
         <v>2026</v>
       </c>
-      <c r="D194" s="9">
-        <v>6971.9766508119646</v>
+      <c r="D194">
+        <v>721.6610564365983</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" s="8">
-        <v>195</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>110</v>
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>113</v>
       </c>
       <c r="C195" s="1">
         <v>2026</v>
       </c>
-      <c r="D195" s="9">
-        <v>5176.3475103154778</v>
+      <c r="D195">
+        <v>4496.6662941062823</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" s="8">
-        <v>196</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>18</v>
+        <v>195</v>
       </c>
       <c r="C196" s="1">
         <v>2026</v>
       </c>
-      <c r="D196" s="9">
-        <v>5209.1038375869393</v>
+      <c r="D196">
+        <v>6350.2893105074763</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" s="8">
-        <v>197</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>111</v>
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>23</v>
       </c>
       <c r="C197" s="1">
         <v>2026</v>
       </c>
-      <c r="D197" s="9">
-        <v>1544.6386331543331</v>
+      <c r="D197">
+        <v>3723.8944750165101</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" s="8">
-        <v>198</v>
-      </c>
-      <c r="B198" s="1"/>
+        <v>197</v>
+      </c>
       <c r="C198" s="1">
         <v>2026</v>
       </c>
-      <c r="D198" s="9">
-        <v>11524.26645523775</v>
+      <c r="D198">
+        <v>4412.1859986074269</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" s="8">
-        <v>199</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C199" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D199" s="9">
-        <v>3461.9229219518602</v>
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>114</v>
+      </c>
+      <c r="C199" s="12">
+        <v>2026</v>
+      </c>
+      <c r="D199">
+        <v>7701.2386902454309</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A200" s="8">
-        <v>200</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C200" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D200" s="9">
-        <v>223.3704585544765</v>
-      </c>
+      <c r="A200" s="18"/>
+      <c r="B200" s="18"/>
+      <c r="C200" s="18"/>
+      <c r="D200" s="18"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A201" s="8">
-        <v>201</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C201" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D201" s="9">
-        <v>1302.7881271715739</v>
-      </c>
+      <c r="A201" s="18"/>
+      <c r="B201" s="18"/>
+      <c r="C201" s="18"/>
+      <c r="D201" s="18"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A202" s="8">
-        <v>202</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C202" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D202" s="9">
-        <v>2754.187203912355</v>
-      </c>
+      <c r="A202" s="18"/>
+      <c r="B202" s="18"/>
+      <c r="C202" s="18"/>
+      <c r="D202" s="18"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A203" s="8">
-        <v>203</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C203" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D203" s="9">
-        <v>884.20877583324909</v>
-      </c>
+      <c r="A203" s="18"/>
+      <c r="B203" s="18"/>
+      <c r="C203" s="18"/>
+      <c r="D203" s="18"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A204" s="8">
-        <v>204</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C204" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D204" s="9">
-        <v>522.25835009664297</v>
-      </c>
+      <c r="A204" s="18"/>
+      <c r="B204" s="18"/>
+      <c r="C204" s="18"/>
+      <c r="D204" s="18"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A205" s="8">
-        <v>205</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C205" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D205" s="9">
-        <v>1606.22439211607</v>
-      </c>
+      <c r="A205" s="18"/>
+      <c r="B205" s="18"/>
+      <c r="C205" s="18"/>
+      <c r="D205" s="18"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A206" s="8">
-        <v>206</v>
-      </c>
-      <c r="B206" s="1"/>
-      <c r="C206" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D206" s="9">
-        <v>2116.5112092643981</v>
-      </c>
+      <c r="A206" s="18"/>
+      <c r="B206" s="18"/>
+      <c r="C206" s="18"/>
+      <c r="D206" s="18"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A207" s="8">
-        <v>207</v>
-      </c>
-      <c r="B207" s="1"/>
-      <c r="C207" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D207" s="9">
-        <v>755.05368263274431</v>
-      </c>
+      <c r="A207" s="18"/>
+      <c r="B207" s="18"/>
+      <c r="C207" s="18"/>
+      <c r="D207" s="18"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A208" s="8">
-        <v>208</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C208" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D208" s="9">
-        <v>40708.200460527092</v>
-      </c>
+      <c r="A208" s="18"/>
+      <c r="B208" s="18"/>
+      <c r="C208" s="18"/>
+      <c r="D208" s="18"/>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="8">
-        <v>209</v>
-      </c>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D209" s="9">
-        <v>19216.072628157679</v>
-      </c>
+      <c r="A209" s="18"/>
+      <c r="B209" s="18"/>
+      <c r="C209" s="18"/>
+      <c r="D209" s="18"/>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A210" s="8">
-        <v>210</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C210" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D210" s="9">
-        <v>360.23156277835369</v>
-      </c>
+      <c r="A210" s="18"/>
+      <c r="B210" s="18"/>
+      <c r="C210" s="18"/>
+      <c r="D210" s="18"/>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="8">
-        <v>211</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C211" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D211" s="9">
-        <v>721.6610564365983</v>
-      </c>
+      <c r="A211" s="18"/>
+      <c r="B211" s="18"/>
+      <c r="C211" s="18"/>
+      <c r="D211" s="18"/>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A212" s="8">
-        <v>212</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C212" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D212" s="9">
-        <v>4496.6662941062823</v>
-      </c>
+      <c r="A212" s="18"/>
+      <c r="B212" s="18"/>
+      <c r="C212" s="18"/>
+      <c r="D212" s="18"/>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="8">
-        <v>213</v>
-      </c>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D213" s="9">
-        <v>6350.2893105074763</v>
-      </c>
+      <c r="A213" s="18"/>
+      <c r="B213" s="18"/>
+      <c r="C213" s="18"/>
+      <c r="D213" s="18"/>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="8">
-        <v>214</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C214" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D214" s="9">
-        <v>3723.8944750165101</v>
-      </c>
+      <c r="A214" s="18"/>
+      <c r="B214" s="18"/>
+      <c r="C214" s="18"/>
+      <c r="D214" s="18"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A215" s="8">
-        <v>215</v>
-      </c>
-      <c r="B215" s="1"/>
-      <c r="C215" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D215" s="9">
-        <v>4412.1859986074269</v>
-      </c>
+      <c r="A215" s="18"/>
+      <c r="B215" s="18"/>
+      <c r="C215" s="18"/>
+      <c r="D215" s="18"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="13">
-        <v>216</v>
-      </c>
-      <c r="B216" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C216" s="14">
-        <v>2026</v>
-      </c>
-      <c r="D216" s="15">
-        <v>7701.2386902454309</v>
-      </c>
+      <c r="A216" s="18"/>
+      <c r="B216" s="18"/>
+      <c r="C216" s="18"/>
+      <c r="D216" s="18"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="18"/>
+      <c r="B217" s="18"/>
+      <c r="C217" s="18"/>
+      <c r="D217" s="18"/>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G218" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="G219" s="5">
         <f>COUNT(Tableau2[FID])</f>
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4321,7 +4138,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -4329,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -4343,7 +4160,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -4357,7 +4174,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -4371,7 +4188,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -4385,7 +4202,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
@@ -4399,7 +4216,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1">
         <v>2025</v>
@@ -4413,7 +4230,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1">
         <v>2025</v>
@@ -4427,7 +4244,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1">
         <v>2025</v>
@@ -4441,7 +4258,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
@@ -4455,7 +4272,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1">
         <v>2025</v>
@@ -4469,7 +4286,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C12" s="1">
         <v>2025</v>
@@ -4477,10 +4294,10 @@
       <c r="D12" s="1">
         <v>707</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="18">
+      <c r="F12" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G12" s="15">
         <f>SUM(D2:D56)</f>
         <v>91066</v>
       </c>
@@ -4490,7 +4307,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C13" s="1">
         <v>2025</v>
@@ -4504,7 +4321,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C14" s="1">
         <v>2025</v>
@@ -4518,7 +4335,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="1">
         <v>2025</v>
@@ -4532,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
@@ -4546,7 +4363,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="1">
         <v>2025</v>
@@ -4560,7 +4377,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C18" s="1">
         <v>2025</v>
@@ -4574,7 +4391,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
@@ -4586,7 +4403,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
@@ -4598,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
@@ -4610,7 +4427,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
@@ -4622,7 +4439,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -4634,7 +4451,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -4646,7 +4463,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
@@ -4658,7 +4475,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
@@ -4670,7 +4487,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1">
@@ -4682,7 +4499,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
@@ -4694,7 +4511,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
@@ -4706,7 +4523,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
@@ -4718,7 +4535,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
@@ -4730,7 +4547,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
@@ -4742,7 +4559,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -4754,7 +4571,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -4766,7 +4583,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -4778,7 +4595,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -4790,7 +4607,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -4802,7 +4619,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -4814,7 +4631,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -4826,7 +4643,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
@@ -4838,7 +4655,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
@@ -4850,7 +4667,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
@@ -4862,7 +4679,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -4874,7 +4691,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -4886,7 +4703,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
@@ -4898,7 +4715,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -4910,7 +4727,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -4922,7 +4739,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -4934,7 +4751,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -4946,7 +4763,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -4958,7 +4775,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -4970,7 +4787,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
@@ -4982,7 +4799,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
@@ -4994,7 +4811,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
@@ -5006,7 +4823,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
@@ -5018,7 +4835,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
@@ -5053,7 +4870,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -5061,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -5075,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -5083,10 +4900,10 @@
       <c r="D3" s="1">
         <v>38</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F3" s="18">
+      <c r="E3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="15">
         <f>SUM(D2:D5)</f>
         <v>4860.3</v>
       </c>
@@ -5096,7 +4913,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -5110,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -5120,72 +4937,72 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="17">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="17">
+      <c r="B6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="14">
         <v>2025</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>969</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="17">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="14">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="14">
+        <v>2025</v>
+      </c>
+      <c r="D8" s="14">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C10" s="14">
         <v>2025</v>
       </c>
-      <c r="D7" s="17">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
-        <v>7</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="17">
-        <v>2025</v>
-      </c>
-      <c r="D8" s="17">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="17">
-        <v>2025</v>
-      </c>
-      <c r="D9" s="17">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
-        <v>9</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="17">
-        <v>2025</v>
-      </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>289</v>
       </c>
     </row>
@@ -5194,18 +5011,18 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" s="1">
         <v>2025</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.35">
-      <c r="G21" s="16" t="s">
-        <v>198</v>
+      <c r="G21" s="13" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -5235,7 +5052,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -5243,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -5257,7 +5074,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -5265,10 +5082,10 @@
       <c r="D3" s="1">
         <v>1881</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="G3" s="18">
+      <c r="F3" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="15">
         <f>SUM(D2:D6)</f>
         <v>14196</v>
       </c>
@@ -5278,7 +5095,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -5292,7 +5109,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -5306,7 +5123,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
@@ -5341,7 +5158,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -5349,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C14" s="1">
         <v>2026</v>
@@ -5363,7 +5180,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
@@ -5371,10 +5188,10 @@
       <c r="D15" s="1">
         <v>8085</v>
       </c>
-      <c r="E15" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="18">
+      <c r="E15" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F15" s="15">
         <f>SUM(D14:D15)</f>
         <v>17385</v>
       </c>
@@ -5405,7 +5222,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -5413,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C2" s="1">
         <v>2026</v>
@@ -5427,7 +5244,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1">
         <v>2026</v>
@@ -5437,10 +5254,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E5" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="18">
+      <c r="E5" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="15">
         <f>SUM(D2,D3)</f>
         <v>930</v>
       </c>
@@ -5461,24 +5278,24 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1">
         <f>('JARDINS FAMILIAUX'!G4)</f>
-        <v>2227302.7899881979</v>
+        <v>2063689.2722669034</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1">
         <f>'JARDINS PARTAGES'!G12</f>
@@ -5487,7 +5304,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1">
         <v>8892.2999999999993</v>
@@ -5495,7 +5312,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B5" s="1">
         <f>(PUC!G3)</f>
@@ -5504,7 +5321,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B6" s="1">
         <f>'CITES FERTILLES'!F15</f>
@@ -5513,7 +5330,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B7" s="1">
         <f>'MASSIFS NOURRICIERS'!F5</f>
@@ -5530,20 +5347,20 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(B2:B7)</f>
-        <v>2359772.0899881977</v>
+        <v>2196158.5722669032</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="20">
+        <v>153</v>
+      </c>
+      <c r="B11" s="17">
         <f>B10/10000</f>
-        <v>235.97720899881978</v>
+        <v>219.61585722669034</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -5552,7 +5369,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B13" s="1">
         <v>337.6</v>
@@ -5560,7 +5377,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B14" s="4">
         <f>B13*100</f>
@@ -5569,7 +5386,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B15" s="4">
         <v>7829.4</v>
@@ -5581,20 +5398,20 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B17" s="6">
         <f>B11/B14</f>
-        <v>6.9898462381166992E-3</v>
+        <v>6.5052090410749504E-3</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="19">
+      <c r="A18" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="16">
         <f>B11/B15</f>
-        <v>3.0139884154446035E-2</v>
+        <v>2.8050151636995216E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5614,24 +5431,24 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B2" s="1">
         <f>COUNT('JARDINS FAMILIAUX'!A:A)</f>
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1">
         <f>COUNTA('JARDINS PARTAGES'!B2:B56)</f>
@@ -5640,7 +5457,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1">
         <f>COUNTA('JARDINS PRODUCTIFS'!B2:B5,'JARDINS PRODUCTIFS'!B11:B11)</f>
@@ -5649,7 +5466,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B5" s="1">
         <f>COUNTA(PUC!B2:B6)</f>
@@ -5658,7 +5475,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B6" s="1">
         <f>COUNTA('CITES FERTILLES'!B14:B15)</f>
@@ -5667,7 +5484,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B7" s="1">
         <f>COUNTA('MASSIFS NOURRICIERS'!B2:B3)</f>
@@ -5676,11 +5493,11 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B10" s="7">
         <f>SUM(B2:B7)</f>
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
